--- a/tables/Datas/item.xlsx
+++ b/tables/Datas/item.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -79,6 +79,9 @@
     </r>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>price</t>
   </si>
   <si>
@@ -140,6 +143,9 @@
     <t>描述</t>
   </si>
   <si>
+    <t>图标ID</t>
+  </si>
+  <si>
     <t>价格</t>
   </si>
   <si>
@@ -378,7 +384,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -394,6 +400,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -726,7 +738,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -750,16 +762,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -774,89 +786,95 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1177,19 +1195,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="12.3833333333333" customWidth="1"/>
-    <col min="5" max="5" width="5.5" customWidth="1"/>
-    <col min="6" max="6" width="18.75" customWidth="1"/>
-    <col min="7" max="7" width="13.1333333333333" customWidth="1"/>
+    <col min="5" max="5" width="8.875" customWidth="1"/>
+    <col min="6" max="6" width="5.5" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="8" max="8" width="13.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:29">
+    <row r="1" s="1" customFormat="1" spans="1:30">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1202,7 +1221,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1211,8 +1230,10 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1"/>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5"/>
       <c r="J1"/>
       <c r="K1"/>
       <c r="L1"/>
@@ -1233,19 +1254,20 @@
       <c r="AA1"/>
       <c r="AB1"/>
       <c r="AC1"/>
+      <c r="AD1"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:29">
+    <row r="2" s="1" customFormat="1" spans="1:30">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="E2" s="4"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="5"/>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
@@ -1266,31 +1288,34 @@
       <c r="AA2"/>
       <c r="AB2"/>
       <c r="AC2"/>
+      <c r="AD2"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:29">
-      <c r="A3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="3" s="2" customFormat="1" spans="1:30">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3"/>
+      <c r="H3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5"/>
       <c r="J3"/>
       <c r="K3"/>
       <c r="L3"/>
@@ -1311,23 +1336,26 @@
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3"/>
+      <c r="AD3"/>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:29">
-      <c r="A4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
+    <row r="4" s="2" customFormat="1" spans="1:30">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="5"/>
       <c r="J4"/>
       <c r="K4"/>
       <c r="L4"/>
@@ -1348,31 +1376,34 @@
       <c r="AA4"/>
       <c r="AB4"/>
       <c r="AC4"/>
+      <c r="AD4"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:29">
+    <row r="5" s="1" customFormat="1" spans="1:30">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="E5" s="7" t="s">
+        <v>19</v>
+      </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5"/>
+        <v>21</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="5"/>
       <c r="J5"/>
       <c r="K5"/>
       <c r="L5"/>
@@ -1393,204 +1424,235 @@
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5"/>
+      <c r="AD5"/>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6" spans="1:30">
       <c r="B6">
         <v>10000</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6">
+        <v>4201101</v>
+      </c>
+      <c r="F6">
         <v>100</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>10001</v>
       </c>
-      <c r="G6" t="b">
+      <c r="H6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7" spans="1:30">
       <c r="B7">
         <v>10001</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7">
+        <v>4201102</v>
+      </c>
+      <c r="F7">
         <v>100</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>10002</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8" spans="1:30">
       <c r="B8">
         <v>10002</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8">
+        <v>4201103</v>
+      </c>
+      <c r="F8">
         <v>100</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>10003</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29">
+    <row r="9" spans="1:30">
       <c r="B9">
         <v>10003</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9">
+        <v>4201104</v>
+      </c>
+      <c r="F9">
         <v>100</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>10004</v>
       </c>
-      <c r="G9" t="s">
-        <v>29</v>
+      <c r="H9" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:29">
+    <row r="10" spans="1:30">
       <c r="B10">
         <v>10004</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E10">
+        <v>4201201</v>
+      </c>
+      <c r="F10">
         <v>100</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>10005</v>
       </c>
-      <c r="G10" t="s">
-        <v>32</v>
+      <c r="H10" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11" spans="1:30">
       <c r="B11">
         <v>10005</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>33</v>
+      <c r="C11" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11">
+        <v>4201202</v>
+      </c>
+      <c r="F11">
         <v>100</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>10006</v>
       </c>
-      <c r="G11" t="s">
-        <v>35</v>
+      <c r="H11" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12" spans="1:30">
       <c r="B12">
         <v>10006</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E12">
+        <v>4201203</v>
+      </c>
+      <c r="F12">
         <v>100</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>10007</v>
       </c>
-      <c r="G12" t="s">
-        <v>38</v>
+      <c r="H12" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:29">
+    <row r="13" spans="1:30">
       <c r="B13">
         <v>10007</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>39</v>
+      <c r="C13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="E13">
+        <v>4201204</v>
+      </c>
+      <c r="F13">
         <v>200</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>10008</v>
       </c>
-      <c r="G13" t="b">
+      <c r="H13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:29">
+    <row r="14" spans="1:30">
       <c r="B14">
         <v>10008</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>40</v>
+      <c r="C14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="E14">
+        <v>4201205</v>
+      </c>
+      <c r="F14">
         <v>300</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>10009</v>
       </c>
-      <c r="G14" t="b">
+      <c r="H14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:29">
+    <row r="15" spans="1:30">
       <c r="B15">
         <v>10009</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>42</v>
+      <c r="C15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="E15">
+        <v>4201206</v>
+      </c>
+      <c r="F15">
         <v>100</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>10000</v>
       </c>
-      <c r="G15" t="b">
+      <c r="H15" t="b">
         <v>1</v>
       </c>
     </row>
